--- a/salidas/empresas/ISRG.xlsx
+++ b/salidas/empresas/ISRG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
@@ -520,7 +532,7 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
@@ -539,7 +551,7 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
@@ -558,7 +570,7 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
@@ -577,7 +589,7 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
@@ -596,7 +608,7 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
@@ -615,7 +627,7 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
@@ -653,7 +665,7 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -691,7 +703,7 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
@@ -710,7 +722,7 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
@@ -729,7 +741,7 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
@@ -767,7 +779,7 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
@@ -786,7 +798,7 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
@@ -805,7 +817,7 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
@@ -824,7 +836,7 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
@@ -843,7 +855,7 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -900,7 +912,7 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
@@ -919,7 +931,7 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
@@ -938,7 +950,7 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,7 +988,7 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -995,7 +1007,7 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
@@ -1014,7 +1026,7 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
@@ -1033,7 +1045,7 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
@@ -1052,7 +1064,7 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,7 +1102,7 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,7 +1159,7 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
@@ -1166,7 +1178,7 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
@@ -1185,7 +1197,7 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,7 +1235,7 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
@@ -1242,7 +1254,7 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
@@ -1261,7 +1273,7 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
@@ -1280,7 +1292,7 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1305,7 +1317,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1330,7 +1342,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1355,7 +1367,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
@@ -1380,7 +1392,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1405,7 +1417,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
@@ -1430,7 +1442,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
@@ -1455,7 +1467,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1480,7 +1492,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
@@ -1505,7 +1517,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1530,7 +1542,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
@@ -1555,7 +1567,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
@@ -1580,7 +1592,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
@@ -1605,7 +1617,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
@@ -1630,7 +1642,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1655,7 +1667,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
@@ -1680,7 +1692,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
@@ -1705,7 +1717,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1730,7 +1742,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
@@ -1755,7 +1767,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
@@ -1784,7 +1796,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
@@ -1813,7 +1825,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
@@ -1842,7 +1854,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
@@ -1871,7 +1883,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
@@ -1900,7 +1912,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
@@ -1929,7 +1941,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
@@ -1958,7 +1970,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
@@ -1987,7 +1999,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
@@ -2016,7 +2028,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -2045,7 +2057,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
@@ -2074,7 +2086,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -2103,7 +2115,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2132,7 +2144,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2161,7 +2173,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
@@ -2190,7 +2202,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
@@ -2219,7 +2231,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
@@ -2248,7 +2260,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
@@ -2277,7 +2289,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
@@ -2306,7 +2318,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
@@ -2335,7 +2347,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
@@ -2364,7 +2376,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
@@ -2393,7 +2405,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
@@ -2422,7 +2434,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
@@ -2451,7 +2463,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
@@ -2480,7 +2492,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
@@ -2509,7 +2521,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
@@ -2538,7 +2550,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2567,7 +2579,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
@@ -2596,7 +2608,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2625,7 +2637,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2654,7 +2666,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -2683,7 +2695,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
@@ -2712,7 +2724,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
@@ -2741,7 +2753,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2770,7 +2782,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
@@ -2799,7 +2811,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
@@ -2828,7 +2840,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
@@ -2857,7 +2869,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
@@ -2886,7 +2898,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
@@ -2915,7 +2927,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2944,7 +2956,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2973,7 +2985,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
@@ -3002,7 +3014,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -3031,7 +3043,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -3060,7 +3072,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
@@ -3089,7 +3101,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
@@ -3118,7 +3130,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
@@ -3147,7 +3159,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -3176,7 +3188,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3205,7 +3217,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
@@ -3234,7 +3246,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
@@ -3263,7 +3275,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
@@ -3292,7 +3304,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3321,7 +3333,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
@@ -3350,7 +3362,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
@@ -3379,7 +3391,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
@@ -3408,7 +3420,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
@@ -3437,7 +3449,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
@@ -3466,7 +3478,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
@@ -3495,7 +3507,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3524,7 +3536,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
@@ -3553,7 +3565,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
@@ -3582,7 +3594,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
@@ -3611,7 +3623,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -3640,7 +3652,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
@@ -3669,7 +3681,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3698,7 +3710,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3727,7 +3739,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
@@ -3756,7 +3768,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
@@ -3785,7 +3797,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -3814,7 +3826,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3843,7 +3855,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
@@ -3872,7 +3884,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3901,7 +3913,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
@@ -3930,7 +3942,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
@@ -3959,7 +3971,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3988,7 +4000,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -4017,7 +4029,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
@@ -4046,7 +4058,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
@@ -4075,7 +4087,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
@@ -4104,7 +4116,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
@@ -4133,7 +4145,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
@@ -4162,7 +4174,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -4191,7 +4203,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -4220,7 +4232,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4249,7 +4261,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4278,7 +4290,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
@@ -4307,7 +4319,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
@@ -4336,7 +4348,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4365,7 +4377,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
@@ -4394,7 +4406,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4423,7 +4435,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
@@ -4452,7 +4464,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
@@ -4481,7 +4493,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4510,7 +4522,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
@@ -4539,7 +4551,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
@@ -4568,7 +4580,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
@@ -4597,7 +4609,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4626,7 +4638,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4655,7 +4667,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4684,7 +4696,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
@@ -4713,7 +4725,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4742,7 +4754,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
@@ -4771,7 +4783,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4800,7 +4812,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
@@ -4829,7 +4841,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4858,7 +4870,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
@@ -4887,7 +4899,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4916,7 +4928,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
@@ -4945,7 +4957,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
@@ -4974,7 +4986,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -5003,7 +5015,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -5032,7 +5044,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
@@ -5061,7 +5073,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
@@ -5090,7 +5102,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
@@ -5119,7 +5131,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5148,7 +5160,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
@@ -5177,7 +5189,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
@@ -5206,7 +5218,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
@@ -5235,7 +5247,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5264,7 +5276,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5293,7 +5305,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
@@ -5322,7 +5334,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5351,7 +5363,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
@@ -5380,7 +5392,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5409,7 +5421,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
@@ -5438,7 +5450,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5467,7 +5479,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
@@ -5496,7 +5508,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5525,7 +5537,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5554,7 +5566,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
@@ -5583,7 +5595,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
@@ -5612,7 +5624,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5641,7 +5653,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5670,7 +5682,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
@@ -5699,7 +5711,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5728,7 +5740,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5757,7 +5769,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5786,7 +5798,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
@@ -5815,7 +5827,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5844,7 +5856,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
@@ -5873,7 +5885,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
@@ -5902,7 +5914,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
@@ -5931,7 +5943,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5960,7 +5972,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
@@ -5989,7 +6001,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -6018,7 +6030,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -6047,7 +6059,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
@@ -6076,7 +6088,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6105,7 +6117,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6134,7 +6146,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
@@ -6163,7 +6175,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6192,7 +6204,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6221,7 +6233,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6250,7 +6262,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6279,7 +6291,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
@@ -6308,7 +6320,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6337,7 +6349,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6366,7 +6378,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6395,7 +6407,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6424,7 +6436,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
@@ -6453,7 +6465,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6482,7 +6494,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
@@ -6511,7 +6523,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6540,7 +6552,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6569,7 +6581,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
@@ -6598,7 +6610,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
@@ -6627,7 +6639,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6656,7 +6668,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6685,7 +6697,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6714,7 +6726,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6743,7 +6755,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6772,7 +6784,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6801,7 +6813,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6830,7 +6842,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
@@ -6859,7 +6871,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6888,7 +6900,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6917,7 +6929,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6946,7 +6958,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6975,7 +6987,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -7004,7 +7016,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7033,7 +7045,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -7062,7 +7074,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7091,7 +7103,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7120,7 +7132,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7149,7 +7161,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7178,32 +7190,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>398.2999877929688</v>
+        <v>399.5199890136719</v>
       </c>
       <c r="C250" t="n">
-        <v>398.2999877929688</v>
+        <v>399.5199890136719</v>
       </c>
       <c r="D250" t="n">
-        <v>40456500</v>
+        <v>42021100</v>
       </c>
       <c r="E250" t="n">
         <v>8.710000000000001</v>
       </c>
       <c r="F250" t="n">
-        <v>45.72904567083452</v>
+        <v>45.86911469732168</v>
       </c>
       <c r="G250" t="n">
         <v>353278038</v>
       </c>
       <c r="H250" t="n">
-        <v>140710638222.924</v>
+        <v>141141637860.5316</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1145174498506471</v>
+        <v>0.1189462561496676</v>
       </c>
     </row>
   </sheetData>
@@ -7235,75 +7247,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40017</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7339,13 +7351,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40107</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7381,13 +7393,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40288</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7423,13 +7435,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40017</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7465,13 +7477,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40107</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7507,13 +7519,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7540,7 +7552,7 @@
       <c r="I7" t="n">
         <v>0.6588888888888889</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="K7" t="n">
@@ -7553,13 +7565,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40288</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7586,7 +7598,7 @@
       <c r="I8" t="n">
         <v>0.8144444444444445</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="K8" t="n">
@@ -7599,13 +7611,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40382</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7632,7 +7644,7 @@
       <c r="I9" t="n">
         <v>0.8777777777777778</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="K9" t="n">
@@ -7645,13 +7657,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40471</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7678,7 +7690,7 @@
       <c r="I10" t="n">
         <v>0.9333333333333333</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="K10" t="n">
@@ -7691,13 +7703,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7724,7 +7736,7 @@
       <c r="I11" t="n">
         <v>1.052222222222222</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="K11" t="n">
@@ -7737,13 +7749,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40653</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7770,7 +7782,7 @@
       <c r="I12" t="n">
         <v>1.104444444444444</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40653</v>
       </c>
       <c r="K12" t="n">
@@ -7783,13 +7795,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40744</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7816,7 +7828,7 @@
       <c r="I13" t="n">
         <v>1.184444444444444</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40744</v>
       </c>
       <c r="K13" t="n">
@@ -7829,13 +7841,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40835</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7862,7 +7874,7 @@
       <c r="I14" t="n">
         <v>1.285555555555556</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40835</v>
       </c>
       <c r="K14" t="n">
@@ -7875,13 +7887,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40945</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7908,7 +7920,7 @@
       <c r="I15" t="n">
         <v>1.366666666666667</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40945</v>
       </c>
       <c r="K15" t="n">
@@ -7921,13 +7933,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41018</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7954,7 +7966,7 @@
       <c r="I16" t="n">
         <v>1.467777777777778</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41018</v>
       </c>
       <c r="K16" t="n">
@@ -7967,13 +7979,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41113</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8000,7 +8012,7 @@
       <c r="I17" t="n">
         <v>1.561111111111111</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41113</v>
       </c>
       <c r="K17" t="n">
@@ -8013,13 +8025,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41200</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8046,7 +8058,7 @@
       <c r="I18" t="n">
         <v>1.717777777777778</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41200</v>
       </c>
       <c r="K18" t="n">
@@ -8059,13 +8071,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41309</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8092,7 +8104,7 @@
       <c r="I19" t="n">
         <v>1.773333333333333</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41309</v>
       </c>
       <c r="K19" t="n">
@@ -8105,13 +8117,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41383</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8138,7 +8150,7 @@
       <c r="I20" t="n">
         <v>1.891111111111111</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41383</v>
       </c>
       <c r="K20" t="n">
@@ -8151,13 +8163,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41477</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8184,7 +8196,7 @@
       <c r="I21" t="n">
         <v>1.907777777777778</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41477</v>
       </c>
       <c r="K21" t="n">
@@ -8197,13 +8209,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41565</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8230,7 +8242,7 @@
       <c r="I22" t="n">
         <v>1.855555555555555</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41565</v>
       </c>
       <c r="K22" t="n">
@@ -8243,13 +8255,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41673</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8276,7 +8288,7 @@
       <c r="I23" t="n">
         <v>1.858888888888889</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41673</v>
       </c>
       <c r="K23" t="n">
@@ -8289,13 +8301,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8322,7 +8334,7 @@
       <c r="I24" t="n">
         <v>1.477777777777778</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="K24" t="n">
@@ -8335,13 +8347,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41844</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8368,7 +8380,7 @@
       <c r="I25" t="n">
         <v>1.352222222222222</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41844</v>
       </c>
       <c r="K25" t="n">
@@ -8381,13 +8393,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41935</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8414,7 +8426,7 @@
       <c r="I26" t="n">
         <v>1.281111111111111</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41935</v>
       </c>
       <c r="K26" t="n">
@@ -8427,13 +8439,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42041</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8460,7 +8472,7 @@
       <c r="I27" t="n">
         <v>1.243333333333333</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42041</v>
       </c>
       <c r="K27" t="n">
@@ -8473,13 +8485,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42116</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8506,7 +8518,7 @@
       <c r="I28" t="n">
         <v>1.403333333333333</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42116</v>
       </c>
       <c r="K28" t="n">
@@ -8519,13 +8531,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42207</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8552,7 +8564,7 @@
       <c r="I29" t="n">
         <v>1.491111111111111</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42207</v>
       </c>
       <c r="K29" t="n">
@@ -8565,13 +8577,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42298</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8598,7 +8610,7 @@
       <c r="I30" t="n">
         <v>1.607777777777778</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42298</v>
       </c>
       <c r="K30" t="n">
@@ -8611,13 +8623,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42402</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8644,7 +8656,7 @@
       <c r="I31" t="n">
         <v>1.724444444444444</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42402</v>
       </c>
       <c r="K31" t="n">
@@ -8657,13 +8669,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42479</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8690,7 +8702,7 @@
       <c r="I32" t="n">
         <v>1.832222222222222</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42479</v>
       </c>
       <c r="K32" t="n">
@@ -8703,13 +8715,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42571</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8736,7 +8748,7 @@
       <c r="I33" t="n">
         <v>1.96</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42571</v>
       </c>
       <c r="K33" t="n">
@@ -8749,13 +8761,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42662</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8782,7 +8794,7 @@
       <c r="I34" t="n">
         <v>2.061111111111111</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42662</v>
       </c>
       <c r="K34" t="n">
@@ -8795,13 +8807,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42772</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8828,7 +8840,7 @@
       <c r="I35" t="n">
         <v>2.076666666666667</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42772</v>
       </c>
       <c r="K35" t="n">
@@ -8841,13 +8853,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42844</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8874,7 +8886,7 @@
       <c r="I36" t="n">
         <v>2.202222222222222</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42844</v>
       </c>
       <c r="K36" t="n">
@@ -8887,13 +8899,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42937</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8920,7 +8932,7 @@
       <c r="I37" t="n">
         <v>2.32</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42937</v>
       </c>
       <c r="K37" t="n">
@@ -8933,13 +8945,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43028</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8966,7 +8978,7 @@
       <c r="I38" t="n">
         <v>2.58</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43028</v>
       </c>
       <c r="K38" t="n">
@@ -8979,13 +8991,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43133</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9012,7 +9024,7 @@
       <c r="I39" t="n">
         <v>1.893333333333333</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43133</v>
       </c>
       <c r="K39" t="n">
@@ -9025,13 +9037,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43208</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9058,7 +9070,7 @@
       <c r="I40" t="n">
         <v>2.187777777777778</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43208</v>
       </c>
       <c r="K40" t="n">
@@ -9071,13 +9083,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43301</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9104,7 +9116,7 @@
       <c r="I41" t="n">
         <v>2.263333333333334</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43301</v>
       </c>
       <c r="K41" t="n">
@@ -9117,13 +9129,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43395</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9150,7 +9162,7 @@
       <c r="I42" t="n">
         <v>2.23</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43395</v>
       </c>
       <c r="K42" t="n">
@@ -9163,13 +9175,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43500</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9196,7 +9208,7 @@
       <c r="I43" t="n">
         <v>3.163333333333334</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43500</v>
       </c>
       <c r="K43" t="n">
@@ -9209,13 +9221,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43574</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9242,7 +9254,7 @@
       <c r="I44" t="n">
         <v>3.203333333333334</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43574</v>
       </c>
       <c r="K44" t="n">
@@ -9255,13 +9267,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43668</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9288,7 +9300,7 @@
       <c r="I45" t="n">
         <v>3.376666666666667</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43668</v>
       </c>
       <c r="K45" t="n">
@@ -9301,13 +9313,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43756</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9334,7 +9346,7 @@
       <c r="I46" t="n">
         <v>3.67</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43756</v>
       </c>
       <c r="K46" t="n">
@@ -9347,13 +9359,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43868</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9380,7 +9392,7 @@
       <c r="I47" t="n">
         <v>3.85</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43868</v>
       </c>
       <c r="K47" t="n">
@@ -9393,13 +9405,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43938</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9426,7 +9438,7 @@
       <c r="I48" t="n">
         <v>3.87</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43938</v>
       </c>
       <c r="K48" t="n">
@@ -9439,13 +9451,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44035</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9472,7 +9484,7 @@
       <c r="I49" t="n">
         <v>3.17</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44035</v>
       </c>
       <c r="K49" t="n">
@@ -9485,13 +9497,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44123</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9518,7 +9530,7 @@
       <c r="I50" t="n">
         <v>2.926666666666667</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44123</v>
       </c>
       <c r="K50" t="n">
@@ -9531,13 +9543,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44237</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9564,7 +9576,7 @@
       <c r="I51" t="n">
         <v>2.936666666666667</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44237</v>
       </c>
       <c r="K51" t="n">
@@ -9577,13 +9589,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44307</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9610,7 +9622,7 @@
       <c r="I52" t="n">
         <v>3.233333333333333</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44307</v>
       </c>
       <c r="K52" t="n">
@@ -9623,13 +9635,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44398</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9656,7 +9668,7 @@
       <c r="I53" t="n">
         <v>4.46</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44398</v>
       </c>
       <c r="K53" t="n">
@@ -9669,13 +9681,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44489</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9702,7 +9714,7 @@
       <c r="I54" t="n">
         <v>4.633333333333333</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44489</v>
       </c>
       <c r="K54" t="n">
@@ -9715,13 +9727,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44595</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9748,7 +9760,7 @@
       <c r="I55" t="n">
         <v>4.656666666666666</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44595</v>
       </c>
       <c r="K55" t="n">
@@ -9761,13 +9773,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9794,7 +9806,7 @@
       <c r="I56" t="n">
         <v>4.486666666666666</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="K56" t="n">
@@ -9807,13 +9819,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44764</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9840,7 +9852,7 @@
       <c r="I57" t="n">
         <v>3.92</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44764</v>
       </c>
       <c r="K57" t="n">
@@ -9853,13 +9865,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44855</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9886,7 +9898,7 @@
       <c r="I58" t="n">
         <v>3.78</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44855</v>
       </c>
       <c r="K58" t="n">
@@ -9899,13 +9911,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9932,7 +9944,7 @@
       <c r="I59" t="n">
         <v>3.649999999999999</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="K59" t="n">
@@ -9945,13 +9957,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45036</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9978,7 +9990,7 @@
       <c r="I60" t="n">
         <v>3.649999999999999</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45036</v>
       </c>
       <c r="K60" t="n">
@@ -9991,13 +10003,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45131</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10024,7 +10036,7 @@
       <c r="I61" t="n">
         <v>3.98</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45131</v>
       </c>
       <c r="K61" t="n">
@@ -10037,13 +10049,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45219</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10070,7 +10082,7 @@
       <c r="I62" t="n">
         <v>4.24</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45219</v>
       </c>
       <c r="K62" t="n">
@@ -10083,13 +10095,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10116,7 +10128,7 @@
       <c r="I63" t="n">
         <v>5.03</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="K63" t="n">
@@ -10129,13 +10141,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45401</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10162,7 +10174,7 @@
       <c r="I64" t="n">
         <v>5.54</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45401</v>
       </c>
       <c r="K64" t="n">
@@ -10175,13 +10187,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10208,7 +10220,7 @@
       <c r="I65" t="n">
         <v>5.82</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="K65" t="n">
@@ -10221,13 +10233,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10254,7 +10266,7 @@
       <c r="I66" t="n">
         <v>6.220000000000001</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="K66" t="n">
@@ -10267,13 +10279,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10300,7 +10312,7 @@
       <c r="I67" t="n">
         <v>6.42</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="K67" t="n">
@@ -10313,13 +10325,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10346,7 +10358,7 @@
       <c r="I68" t="n">
         <v>6.83</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="K68" t="n">
@@ -10359,13 +10371,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10392,7 +10404,7 @@
       <c r="I69" t="n">
         <v>7.180000000000001</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="K69" t="n">
@@ -10405,13 +10417,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45952</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10438,7 +10450,7 @@
       <c r="I70" t="n">
         <v>7.570000000000001</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45952</v>
       </c>
       <c r="K70" t="n">
@@ -10451,13 +10463,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46056</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10484,7 +10496,7 @@
       <c r="I71" t="n">
         <v>7.87</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46056</v>
       </c>
       <c r="K71" t="n">
@@ -10497,13 +10509,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10530,7 +10542,7 @@
       <c r="I72" t="n">
         <v>8.23</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="K72" t="n">
@@ -10543,13 +10555,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46224</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10576,7 +10588,7 @@
       <c r="I73" t="n">
         <v>8.710000000000001</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46224</v>
       </c>
       <c r="K73" t="n">
@@ -10613,52 +10625,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40011</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40017</v>
       </c>
       <c r="C2" t="n">
@@ -10687,10 +10699,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40101</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40107</v>
       </c>
       <c r="C3" t="n">
@@ -10719,10 +10731,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40199</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40207</v>
       </c>
       <c r="C4" t="n">
@@ -10751,10 +10763,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40283</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40288</v>
       </c>
       <c r="C5" t="n">
@@ -10783,10 +10795,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40371</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40382</v>
       </c>
       <c r="C6" t="n">
@@ -10815,10 +10827,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40459</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40471</v>
       </c>
       <c r="C7" t="n">
@@ -10847,10 +10859,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40563</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40575</v>
       </c>
       <c r="C8" t="n">
@@ -10879,10 +10891,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40648</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40653</v>
       </c>
       <c r="C9" t="n">
@@ -10911,10 +10923,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40738</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40744</v>
       </c>
       <c r="C10" t="n">
@@ -10943,10 +10955,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40829</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40835</v>
       </c>
       <c r="C11" t="n">
@@ -10975,10 +10987,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40928</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40945</v>
       </c>
       <c r="C12" t="n">
@@ -11007,10 +11019,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41012</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41018</v>
       </c>
       <c r="C13" t="n">
@@ -11039,10 +11051,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41106</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41113</v>
       </c>
       <c r="C14" t="n">
@@ -11071,10 +11083,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41192</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41200</v>
       </c>
       <c r="C15" t="n">
@@ -11103,10 +11115,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41292</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41309</v>
       </c>
       <c r="C16" t="n">
@@ -11135,10 +11147,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41374</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41383</v>
       </c>
       <c r="C17" t="n">
@@ -11167,10 +11179,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41465</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41477</v>
       </c>
       <c r="C18" t="n">
@@ -11199,10 +11211,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41555</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41565</v>
       </c>
       <c r="C19" t="n">
@@ -11231,10 +11243,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41656</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41673</v>
       </c>
       <c r="C20" t="n">
@@ -11263,10 +11275,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41743</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41754</v>
       </c>
       <c r="C21" t="n">
@@ -11295,10 +11307,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41834</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41844</v>
       </c>
       <c r="C22" t="n">
@@ -11327,10 +11339,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41925</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41935</v>
       </c>
       <c r="C23" t="n">
@@ -11359,10 +11371,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42020</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42041</v>
       </c>
       <c r="C24" t="n">
@@ -11391,10 +11403,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42111</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42116</v>
       </c>
       <c r="C25" t="n">
@@ -11423,10 +11435,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42201</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42207</v>
       </c>
       <c r="C26" t="n">
@@ -11455,10 +11467,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42292</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42298</v>
       </c>
       <c r="C27" t="n">
@@ -11487,10 +11499,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42388</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42402</v>
       </c>
       <c r="C28" t="n">
@@ -11519,10 +11531,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42475</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42479</v>
       </c>
       <c r="C29" t="n">
@@ -11551,10 +11563,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42566</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42571</v>
       </c>
       <c r="C30" t="n">
@@ -11583,10 +11595,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42656</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42662</v>
       </c>
       <c r="C31" t="n">
@@ -11615,10 +11627,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42755</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42772</v>
       </c>
       <c r="C32" t="n">
@@ -11647,10 +11659,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42839</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42844</v>
       </c>
       <c r="C33" t="n">
@@ -11679,10 +11691,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42934</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42937</v>
       </c>
       <c r="C34" t="n">
@@ -11711,10 +11723,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43025</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43028</v>
       </c>
       <c r="C35" t="n">
@@ -11743,10 +11755,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43119</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43133</v>
       </c>
       <c r="C36" t="n">
@@ -11775,10 +11787,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43203</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43208</v>
       </c>
       <c r="C37" t="n">
@@ -11807,10 +11819,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43298</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43301</v>
       </c>
       <c r="C38" t="n">
@@ -11839,10 +11851,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43389</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43395</v>
       </c>
       <c r="C39" t="n">
@@ -11871,10 +11883,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43483</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43500</v>
       </c>
       <c r="C40" t="n">
@@ -11903,10 +11915,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43571</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43574</v>
       </c>
       <c r="C41" t="n">
@@ -11935,10 +11947,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43662</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43668</v>
       </c>
       <c r="C42" t="n">
@@ -11967,10 +11979,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43753</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43756</v>
       </c>
       <c r="C43" t="n">
@@ -11999,10 +12011,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43847</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43868</v>
       </c>
       <c r="C44" t="n">
@@ -12031,10 +12043,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43935</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43938</v>
       </c>
       <c r="C45" t="n">
@@ -12063,10 +12075,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44032</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44035</v>
       </c>
       <c r="C46" t="n">
@@ -12095,10 +12107,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44118</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44123</v>
       </c>
       <c r="C47" t="n">
@@ -12127,10 +12139,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44211</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44237</v>
       </c>
       <c r="C48" t="n">
@@ -12159,10 +12171,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44302</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44307</v>
       </c>
       <c r="C49" t="n">
@@ -12191,10 +12203,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44392</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44398</v>
       </c>
       <c r="C50" t="n">
@@ -12223,10 +12235,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44483</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44489</v>
       </c>
       <c r="C51" t="n">
@@ -12255,10 +12267,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44587</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44595</v>
       </c>
       <c r="C52" t="n">
@@ -12287,10 +12299,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44670</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44673</v>
       </c>
       <c r="C53" t="n">
@@ -12319,10 +12331,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44761</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44764</v>
       </c>
       <c r="C54" t="n">
@@ -12351,10 +12363,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44852</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44855</v>
       </c>
       <c r="C55" t="n">
@@ -12383,10 +12395,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44964</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="C56" t="n">
@@ -12415,10 +12427,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45033</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45036</v>
       </c>
       <c r="C57" t="n">
@@ -12447,10 +12459,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45125</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45131</v>
       </c>
       <c r="C58" t="n">
@@ -12479,10 +12491,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45215</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45219</v>
       </c>
       <c r="C59" t="n">
@@ -12511,10 +12523,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45316</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="C60" t="n">
@@ -12543,10 +12555,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45397</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45401</v>
       </c>
       <c r="C61" t="n">
@@ -12575,10 +12587,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45489</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45492</v>
       </c>
       <c r="C62" t="n">
@@ -12607,10 +12619,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45580</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45583</v>
       </c>
       <c r="C63" t="n">
@@ -12639,10 +12651,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45684</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="C64" t="n">
@@ -12671,10 +12683,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45762</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45770</v>
       </c>
       <c r="C65" t="n">
@@ -12703,10 +12715,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45855</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45861</v>
       </c>
       <c r="C66" t="n">
@@ -12735,10 +12747,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45946</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45952</v>
       </c>
       <c r="C67" t="n">
@@ -12767,10 +12779,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46050</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46056</v>
       </c>
       <c r="C68" t="n">
@@ -12799,10 +12811,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46127</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46134</v>
       </c>
       <c r="C69" t="n">
@@ -12831,10 +12843,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46219</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46224</v>
       </c>
       <c r="C70" t="n">
@@ -12881,12 +12893,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>
